--- a/jogos_2025-01-28.xlsx
+++ b/jogos_2025-01-28.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,16 +1417,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.75</v>
       </c>
-      <c r="O8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.54</v>
-      </c>
       <c r="T8" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="X8" t="n">
-        <v>4.55</v>
+        <v>3.32</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.26</v>
+        <v>3.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['7', '65', '79', '90+2']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45685.66666666666</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>2.75</v>
+        <v>3.54</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>3.32</v>
+        <v>4.55</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.46</v>
+        <v>2.26</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['7', '65', '79', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45685.66666666666</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="P10" t="n">
         <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
@@ -1731,25 +1731,25 @@
         <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
         <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Y10" t="n">
         <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC10" t="n">
         <v>1.73</v>
@@ -1759,25 +1759,25 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['87', '90', '90+5']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.62</v>
       </c>
-      <c r="AI10" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45685.69791666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1839,13 +1839,13 @@
         <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
         <v>1.5</v>
@@ -1860,13 +1860,13 @@
         <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="Y11" t="n">
         <v>2.3</v>
@@ -1875,38 +1875,38 @@
         <v>1.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['45+1']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45685.69791666666</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Carlisle United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
         <v>1.33</v>
@@ -1995,47 +1995,47 @@
         <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
         <v>1.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45685.69791666666</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2077,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
         <v>3.4</v>
@@ -2103,7 +2103,7 @@
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.5</v>
@@ -2118,25 +2118,25 @@
         <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC13" t="n">
         <v>1.91</v>
@@ -2146,25 +2146,25 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['90+7']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
         <v>1.48</v>
       </c>
       <c r="AI13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45685.69791666666</v>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.75</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P14" t="n">
         <v>2.1</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q14" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
@@ -2247,19 +2247,19 @@
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="n">
         <v>3.4</v>
@@ -2268,14 +2268,14 @@
         <v>1.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['12', '17']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45685.69791666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
         <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
         <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
@@ -2370,59 +2370,59 @@
         <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.33</v>
       </c>
-      <c r="X15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['12', '17']</t>
+          <t>['10', '29', '90+2']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69', '71']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45685.69791666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2</v>
       </c>
-      <c r="P16" t="n">
+      <c r="AD16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['13', '36']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH16" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="AI16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>3.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['11']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>3.75</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45685.69791666666</v>
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2604,43 +2604,43 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="N17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.5</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
         <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="Y17" t="n">
         <v>1.8</v>
@@ -2649,38 +2649,38 @@
         <v>1.91</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['27', '90+3']</t>
+          <t>['36', '82', '90+1']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.35</v>
+        <v>1.77</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45685.69791666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="AA18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>3.2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45685.69791666666</v>
@@ -2836,19 +2836,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -2862,43 +2862,43 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
         <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="Y19" t="n">
         <v>1.8</v>
@@ -2907,38 +2907,38 @@
         <v>1.91</v>
       </c>
       <c r="AA19" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['36', '82', '90+1']</t>
+          <t>['27', '90+3']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45685.69791666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
@@ -3015,59 +3015,59 @@
         <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
         <v>1.06</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X20" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['32', '57']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI20" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['87', '90', '90+5']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['7']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45685.69791666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,109 +3094,109 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hamilton Academical</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>3</v>
       </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
       <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['3', '7', '31']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.4</v>
       </c>
-      <c r="M21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['3', '44', '83']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['8']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH21" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45685.69791666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,23 +3223,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Carlisle United</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="P22" t="n">
         <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
         <v>1.33</v>
@@ -3294,38 +3294,38 @@
         <v>2.05</v>
       </c>
       <c r="AA22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>2.88</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>3.2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45685.69791666666</v>
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P23" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.4</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['10', '29', '90+2']</t>
+          <t>['47', '56']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['69', '71']</t>
+          <t>['5', '7', '14', '34', '64', '78']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45685.69791666666</v>
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
         <v>1</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
         <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['65', '90+5']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45685.69791666666</v>
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>7</v>
+      </c>
+      <c r="O25" t="n">
         <v>2</v>
       </c>
-      <c r="H25" t="n">
-        <v>6</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="P25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>7</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>4</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['47', '56']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['5', '7', '14', '34', '64', '78']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45685.69791666666</v>
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="R26" t="n">
         <v>1.33</v>
@@ -3795,53 +3795,53 @@
         <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['65', '90+5']</t>
+          <t>['3', '44', '83']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AG26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI26" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45685.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3883,94 +3883,94 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>6</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>7</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="AD27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['53', '69']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['7', '43']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['10']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>4</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45685.69791666666</v>
@@ -3997,109 +3997,109 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>2</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.2</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="AD28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['55', '90']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['13', '18', '71']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>2.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['13', '36']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45685.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4141,10 +4141,10 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="P29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>7</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2</v>
-      </c>
       <c r="AD29" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['53', '69']</t>
+          <t>['7', '43']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45685.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
         <v>3.1</v>
@@ -4293,53 +4293,53 @@
         <v>2.88</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T30" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
         <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X30" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AA30" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4351,13 +4351,13 @@
         <v>1.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AI30" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45685.69791666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hamilton Academical</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,22 +4410,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="O31" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.88</v>
+        <v>6.5</v>
       </c>
       <c r="R31" t="n">
         <v>1.4</v>
@@ -4434,19 +4434,19 @@
         <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Y31" t="n">
         <v>1.83</v>
@@ -4455,38 +4455,38 @@
         <v>1.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['3', '7', '31']</t>
-        </is>
-      </c>
       <c r="AG31" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45685.69791666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,19 +4513,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W32" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="X32" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD32" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+7']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['32', '57']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45685.69791666666</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
         <v>2.88</v>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>2.25</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['55', '90']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['13', '18', '71']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45685.69791666666</v>
